--- a/template.xlsx
+++ b/template.xlsx
@@ -278,7 +278,7 @@
     <t>อบรม</t>
   </si>
   <si>
-    <t>กรกฏาคม</t>
+    <t>กรกฎาคม</t>
   </si>
   <si>
     <t>สิงหาคม</t>
@@ -2407,7 +2407,7 @@
         </row>
         <row r="14">
           <cell r="AS14" t="str">
-            <v>กรกฏาคม</v>
+            <v>กรกฎาคม</v>
           </cell>
         </row>
         <row r="15">
@@ -2526,7 +2526,7 @@
         </row>
         <row r="14">
           <cell r="AS14" t="str">
-            <v>กรกฏาคม</v>
+            <v>กรกฎาคม</v>
           </cell>
           <cell r="AY14" t="str">
             <v>NTV</v>
